--- a/students.xlsx
+++ b/students.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,11 @@
           <t>점수</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -443,6 +448,11 @@
       <c r="B2" t="n">
         <v>80</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -453,6 +463,11 @@
       <c r="B3" t="n">
         <v>90</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +478,11 @@
       <c r="B4" t="n">
         <v>85</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -473,6 +493,11 @@
       <c r="B5" t="n">
         <v>100</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -483,6 +508,11 @@
       <c r="B6" t="n">
         <v>95</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -492,6 +522,11 @@
       </c>
       <c r="B7" t="n">
         <v>40</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
     </row>
   </sheetData>
